--- a/results/monthly_investor_report_2026-09-03.xlsx
+++ b/results/monthly_investor_report_2026-09-03.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1085,16 +1085,16 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09058627837803448</v>
+        <v>0.09058627837803444</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9058.627837803448</v>
+        <v>9058.627837803444</v>
       </c>
       <c r="F23" s="7" t="n">
         <v>0.0919577026412617</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>833.0106050465848</v>
+        <v>833.0106050465845</v>
       </c>
       <c r="H23" s="8" t="n">
         <v>415.2169164293397</v>
@@ -1103,7 +1103,7 @@
         <v>357.1530283216292</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>1.513917794776732</v>
+        <v>1.513917794776729</v>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1455,7 +1455,7 @@
         <v>236.4900906566582</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>255.0697174304946</v>
+        <v>255.0697174304947</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>205.5799942016602</v>
@@ -1611,10 +1611,10 @@
         <v>93</v>
       </c>
       <c r="E11" s="19" t="n">
-        <v>-0.0794520528549532</v>
+        <v>-0.0794520528549533</v>
       </c>
       <c r="F11" s="19" t="n">
-        <v>-0.002145890072864</v>
+        <v>-0.0021458900728641</v>
       </c>
       <c r="G11" s="19" t="n">
         <v>0.0870869998031074</v>
@@ -1623,7 +1623,7 @@
         <v>85.61095908448935</v>
       </c>
       <c r="I11" s="18" t="n">
-        <v>92.80043222322365</v>
+        <v>92.80043222322364</v>
       </c>
       <c r="J11" s="18" t="n">
         <v>101.099090981689</v>
@@ -1668,7 +1668,7 @@
         <v>71.55000305175781</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.1195456698956569</v>
+        <v>-0.1195456698956567</v>
       </c>
       <c r="F12" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -1677,7 +1677,7 @@
         <v>0.0515933324042807</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>62.99651000589913</v>
+        <v>62.99651000589914</v>
       </c>
       <c r="I12" s="18" t="n">
         <v>68.92487147501316</v>
@@ -1686,7 +1686,7 @@
         <v>75.24150614273445</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>62.99651000589913</v>
+        <v>62.99651000589914</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>-0.0609999645366716</v>
       </c>
       <c r="F13" s="19" t="n">
-        <v>-0.0447738760747383</v>
+        <v>-0.0447738760747384</v>
       </c>
       <c r="G13" s="19" t="n">
         <v>0.0704908343640927</v>
@@ -1788,7 +1788,7 @@
         <v>0.0919577026412617</v>
       </c>
       <c r="G14" s="16" t="n">
-        <v>0.1760202809935627</v>
+        <v>0.1760202809935624</v>
       </c>
       <c r="H14" s="15" t="n">
         <v>377.9423233695652</v>
@@ -1797,7 +1797,7 @@
         <v>415.2169164293397</v>
       </c>
       <c r="J14" s="15" t="n">
-        <v>447.1817118478022</v>
+        <v>447.1817118478021</v>
       </c>
       <c r="K14" s="15" t="n">
         <v>357.1530283216292</v>
@@ -1839,7 +1839,7 @@
         <v>131.3999938964844</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-0.0217475887738314</v>
+        <v>-0.0217475887738313</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>0.0331174361060366</v>
@@ -1899,7 +1899,7 @@
         <v>-0.0508568307647213</v>
       </c>
       <c r="F16" s="19" t="n">
-        <v>-0.0154185299195158</v>
+        <v>-0.0154185299195159</v>
       </c>
       <c r="G16" s="19" t="n">
         <v>0.06315792247529731</v>
@@ -1908,13 +1908,13 @@
         <v>19.19167423021244</v>
       </c>
       <c r="I16" s="18" t="n">
-        <v>19.90823664896895</v>
+        <v>19.90823664896894</v>
       </c>
       <c r="J16" s="18" t="n">
         <v>21.4970524624379</v>
       </c>
       <c r="K16" s="18" t="n">
-        <v>19.11551570387917</v>
+        <v>19.11551570387916</v>
       </c>
       <c r="L16" s="17" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2134,10 +2134,10 @@
         <v>0.0504854072644873</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.1449735126798115</v>
+        <v>0.1449735126798117</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1809107991212859</v>
+        <v>0.1809107991212861</v>
       </c>
       <c r="H4" s="16" t="n">
         <v>0.3469524036816227</v>
@@ -2180,7 +2180,7 @@
         <v>0.6237541322454139</v>
       </c>
       <c r="G5" s="16" t="n">
-        <v>0.7620523625301359</v>
+        <v>0.7620523625301361</v>
       </c>
       <c r="H5" s="16" t="n">
         <v>0.200899625699457</v>
@@ -2280,7 +2280,7 @@
         <v>0.0167392005313508</v>
       </c>
       <c r="K7" s="19" t="n">
-        <v>-0.002145890072864</v>
+        <v>-0.0021458900728641</v>
       </c>
     </row>
     <row r="8">
@@ -2352,7 +2352,7 @@
         <v>-0.06588350424950069</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.2847325049290004</v>
+        <v>0.2847325049290006</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>0.283111231226671</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="J9" s="19" t="n">
-        <v>0.022420600998482</v>
+        <v>0.0224206009984821</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>-0.0447738760747383</v>
+        <v>-0.0447738760747384</v>
       </c>
     </row>
     <row r="10">
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="J10" s="16" t="n">
-        <v>0.0303707714376999</v>
+        <v>0.0303707714377</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>0.0919577026412617</v>
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.0009881649204468001</v>
+        <v>-0.000988164920447</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.0297505198989361</v>
+        <v>-0.0297505198989362</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.0830208479232221</v>
+        <v>0.0830208479232219</v>
       </c>
       <c r="H12" s="19" t="n">
         <v>-0.0151103504099816</v>
@@ -2495,7 +2495,7 @@
         <v>0.0273116628828433</v>
       </c>
       <c r="K12" s="19" t="n">
-        <v>-0.0154185299195158</v>
+        <v>-0.0154185299195159</v>
       </c>
     </row>
     <row r="13">
@@ -2581,7 +2581,7 @@
         <v>0.020767963471301</v>
       </c>
       <c r="K14" s="24" t="n">
-        <v>0.0163071580494242</v>
+        <v>0.0163071580494245</v>
       </c>
     </row>
     <row r="15">
@@ -2604,7 +2604,7 @@
         </is>
       </c>
       <c r="E15" s="24" t="n">
-        <v>-0.08859562778512679</v>
+        <v>-0.0885956277851266</v>
       </c>
       <c r="F15" s="24" t="n">
         <v>-0.1366071213416904</v>
@@ -2621,10 +2621,10 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0188806590576912</v>
+        <v>0.0188806590576913</v>
       </c>
       <c r="K15" s="24" t="n">
-        <v>0.0258272542822017</v>
+        <v>0.0258272542822022</v>
       </c>
     </row>
     <row r="16">
@@ -2667,7 +2667,7 @@
         <v>0.0184925189907912</v>
       </c>
       <c r="K16" s="24" t="n">
-        <v>0.1028940851473592</v>
+        <v>0.1028940851473593</v>
       </c>
     </row>
     <row r="17">
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="J17" s="24" t="n">
-        <v>0.0221933836514507</v>
+        <v>0.0221933836514506</v>
       </c>
       <c r="K17" s="24" t="n">
         <v>0.0228670835813538</v>
@@ -2779,7 +2779,7 @@
         <v>-0.09429154071230859</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>-0.1398838736761376</v>
+        <v>-0.1398838736761375</v>
       </c>
       <c r="G19" s="24" t="n">
         <v>-0.2024237230061375</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.0122421878126867</v>
+        <v>0.0122421878126869</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>0.029948947983406</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-05 06:24</t>
+          <t>Son Güncelleme: 2026-09-06 06:34</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3468,7 +3468,7 @@
         <v>216.3999938964844</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>0.09847712637809325</v>
+        <v>0.09847712637809347</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>286208.4782341635</v>

--- a/results/monthly_investor_report_2026-09-03.xlsx
+++ b/results/monthly_investor_report_2026-09-03.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-06 06:34</t>
+          <t>Son Güncelleme: 2026-09-07 06:42</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
